--- a/public/sap-reporting/expansion-150-downloads/EXT-SD09-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-SD09-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R4b71b19c241f4eff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rbc9f11fc74a24c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rc0bf9d790e5748c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R522c4c0d21494cd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rbcfb4778bb764647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rdbf5cf85fad24300"/>
   </x:sheets>
 </x:workbook>
 </file>
